--- a/data/nzd0317/nzd0317.xlsx
+++ b/data/nzd0317/nzd0317.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P532"/>
+  <dimension ref="A1:P534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28832,7 +28832,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>425.21</v>
+        <v>423.26</v>
       </c>
       <c r="C527" t="n">
         <v>417.93</v>
@@ -28886,7 +28886,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>430.68</v>
+        <v>423.26</v>
       </c>
       <c r="C528" t="n">
         <v>419.41</v>
@@ -28940,7 +28940,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>430.68</v>
+        <v>423.26</v>
       </c>
       <c r="C529" t="n">
         <v>419.41</v>
@@ -28994,7 +28994,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>435.09</v>
+        <v>423.62</v>
       </c>
       <c r="C530" t="n">
         <v>422.33</v>
@@ -29048,7 +29048,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>435.09</v>
+        <v>423.62</v>
       </c>
       <c r="C531" t="n">
         <v>422.33</v>
@@ -29102,7 +29102,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>435.09</v>
+        <v>423.62</v>
       </c>
       <c r="C532" t="n">
         <v>422.33</v>
@@ -29146,6 +29146,114 @@
       <c r="P532" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:18:43+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>422.31</v>
+      </c>
+      <c r="C533" t="n">
+        <v>423.75</v>
+      </c>
+      <c r="D533" t="n">
+        <v>390.38</v>
+      </c>
+      <c r="E533" t="n">
+        <v>377.81</v>
+      </c>
+      <c r="F533" t="n">
+        <v>375.69</v>
+      </c>
+      <c r="G533" t="n">
+        <v>374.75</v>
+      </c>
+      <c r="H533" t="n">
+        <v>375.32</v>
+      </c>
+      <c r="I533" t="n">
+        <v>377.17</v>
+      </c>
+      <c r="J533" t="n">
+        <v>373.08</v>
+      </c>
+      <c r="K533" t="n">
+        <v>366.93</v>
+      </c>
+      <c r="L533" t="n">
+        <v>366.29</v>
+      </c>
+      <c r="M533" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="N533" t="n">
+        <v>379.05</v>
+      </c>
+      <c r="O533" t="n">
+        <v>394.37</v>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:18:39+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>420.6</v>
+      </c>
+      <c r="C534" t="n">
+        <v>424.42</v>
+      </c>
+      <c r="D534" t="n">
+        <v>390.59</v>
+      </c>
+      <c r="E534" t="n">
+        <v>378.16</v>
+      </c>
+      <c r="F534" t="n">
+        <v>376.16</v>
+      </c>
+      <c r="G534" t="n">
+        <v>374.8</v>
+      </c>
+      <c r="H534" t="n">
+        <v>375.42</v>
+      </c>
+      <c r="I534" t="n">
+        <v>377.41</v>
+      </c>
+      <c r="J534" t="n">
+        <v>373.76</v>
+      </c>
+      <c r="K534" t="n">
+        <v>367.93</v>
+      </c>
+      <c r="L534" t="n">
+        <v>366.44</v>
+      </c>
+      <c r="M534" t="n">
+        <v>375.45</v>
+      </c>
+      <c r="N534" t="n">
+        <v>379.07</v>
+      </c>
+      <c r="O534" t="n">
+        <v>393.38</v>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29160,7 +29268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B557"/>
+  <dimension ref="A1:B560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34733,6 +34841,36 @@
       </c>
       <c r="B557" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -34901,28 +35039,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>1.432441585582224</v>
+        <v>1.399639216306093</v>
       </c>
       <c r="J2" t="n">
+        <v>533</v>
+      </c>
+      <c r="K2" t="n">
         <v>531</v>
       </c>
-      <c r="K2" t="n">
-        <v>529</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.3173375724680507</v>
+        <v>0.3047562375254229</v>
       </c>
       <c r="M2" t="n">
-        <v>11.55729758907159</v>
+        <v>11.70352168936567</v>
       </c>
       <c r="N2" t="n">
-        <v>235.8679228493305</v>
+        <v>239.5555341898392</v>
       </c>
       <c r="O2" t="n">
-        <v>15.35799214901904</v>
+        <v>15.47758166477694</v>
       </c>
       <c r="P2" t="n">
-        <v>404.8871958862617</v>
+        <v>405.2659876313965</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34979,28 +35117,28 @@
         <v>0.0436</v>
       </c>
       <c r="I3" t="n">
-        <v>1.120744039259919</v>
+        <v>1.129472192739746</v>
       </c>
       <c r="J3" t="n">
+        <v>533</v>
+      </c>
+      <c r="K3" t="n">
         <v>531</v>
       </c>
-      <c r="K3" t="n">
-        <v>529</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2064569505109093</v>
+        <v>0.2097788424944168</v>
       </c>
       <c r="M3" t="n">
-        <v>13.72608808318345</v>
+        <v>13.7284284104475</v>
       </c>
       <c r="N3" t="n">
-        <v>256.4182052182044</v>
+        <v>256.0367462682324</v>
       </c>
       <c r="O3" t="n">
-        <v>16.01306358003379</v>
+        <v>16.00114827967769</v>
       </c>
       <c r="P3" t="n">
-        <v>381.4405230397411</v>
+        <v>381.3391173607345</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35057,28 +35195,28 @@
         <v>0.0762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1075486969895723</v>
+        <v>0.1092974102363326</v>
       </c>
       <c r="J4" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K4" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007151439876577292</v>
+        <v>0.007433117191984584</v>
       </c>
       <c r="M4" t="n">
-        <v>7.392632193469288</v>
+        <v>7.375690064157758</v>
       </c>
       <c r="N4" t="n">
-        <v>85.20082064172816</v>
+        <v>84.90394970256378</v>
       </c>
       <c r="O4" t="n">
-        <v>9.230429060543619</v>
+        <v>9.214333926148095</v>
       </c>
       <c r="P4" t="n">
-        <v>385.085024805274</v>
+        <v>385.0647053620334</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35135,28 +35273,28 @@
         <v>0.0934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3590822767367497</v>
+        <v>-0.360734409066316</v>
       </c>
       <c r="J5" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K5" t="n">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1125856706195791</v>
+        <v>0.1141650499396646</v>
       </c>
       <c r="M5" t="n">
-        <v>5.815234832383202</v>
+        <v>5.799752857425372</v>
       </c>
       <c r="N5" t="n">
-        <v>53.87691363794078</v>
+        <v>53.69462630175356</v>
       </c>
       <c r="O5" t="n">
-        <v>7.340089484327884</v>
+        <v>7.327661721296471</v>
       </c>
       <c r="P5" t="n">
-        <v>390.0028653151832</v>
+        <v>390.0220920329857</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35213,28 +35351,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.42537143753231</v>
+        <v>-0.4274959024041129</v>
       </c>
       <c r="J6" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K6" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1251489333241578</v>
+        <v>0.1269531131685571</v>
       </c>
       <c r="M6" t="n">
-        <v>6.139275045388986</v>
+        <v>6.122710882340565</v>
       </c>
       <c r="N6" t="n">
-        <v>67.11005216758385</v>
+        <v>66.89250741436608</v>
       </c>
       <c r="O6" t="n">
-        <v>8.192072519673141</v>
+        <v>8.178783981397606</v>
       </c>
       <c r="P6" t="n">
-        <v>390.4099024051972</v>
+        <v>390.4345864236318</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35291,28 +35429,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4137706849891946</v>
+        <v>-0.4159607985604809</v>
       </c>
       <c r="J7" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K7" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1239916955358285</v>
+        <v>0.1258409913188682</v>
       </c>
       <c r="M7" t="n">
-        <v>6.045031668543082</v>
+        <v>6.030318224941505</v>
       </c>
       <c r="N7" t="n">
-        <v>64.17694125944367</v>
+        <v>63.97237336967645</v>
       </c>
       <c r="O7" t="n">
-        <v>8.011051195657387</v>
+        <v>7.998273149228929</v>
       </c>
       <c r="P7" t="n">
-        <v>389.0416006102508</v>
+        <v>389.0670482930295</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35369,28 +35507,28 @@
         <v>0.0761</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4427653371697167</v>
+        <v>-0.4459061543081422</v>
       </c>
       <c r="J8" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K8" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1355948410654649</v>
+        <v>0.1379476701852816</v>
       </c>
       <c r="M8" t="n">
-        <v>6.303980499415703</v>
+        <v>6.291577498971161</v>
       </c>
       <c r="N8" t="n">
-        <v>66.30791388473335</v>
+        <v>66.13411446734796</v>
       </c>
       <c r="O8" t="n">
-        <v>8.142967142555184</v>
+        <v>8.132288390566824</v>
       </c>
       <c r="P8" t="n">
-        <v>391.7785714671452</v>
+        <v>391.8150656680037</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35447,28 +35585,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5500224243935191</v>
+        <v>-0.5516795307800613</v>
       </c>
       <c r="J9" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K9" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1865715768620461</v>
+        <v>0.1884986658156077</v>
       </c>
       <c r="M9" t="n">
-        <v>6.240773641116788</v>
+        <v>6.223936500481925</v>
       </c>
       <c r="N9" t="n">
-        <v>69.98075228918123</v>
+        <v>69.738732265999</v>
       </c>
       <c r="O9" t="n">
-        <v>8.365449915526435</v>
+        <v>8.350971935409614</v>
       </c>
       <c r="P9" t="n">
-        <v>394.453008259065</v>
+        <v>394.4722623389672</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35525,28 +35663,28 @@
         <v>0.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6109043943742475</v>
+        <v>-0.6130210853393976</v>
       </c>
       <c r="J10" t="n">
+        <v>533</v>
+      </c>
+      <c r="K10" t="n">
         <v>531</v>
       </c>
-      <c r="K10" t="n">
-        <v>529</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1979155402175182</v>
+        <v>0.2000529374453145</v>
       </c>
       <c r="M10" t="n">
-        <v>6.713434359581981</v>
+        <v>6.697083186968561</v>
       </c>
       <c r="N10" t="n">
-        <v>80.25736770750459</v>
+        <v>79.98984840701834</v>
       </c>
       <c r="O10" t="n">
-        <v>8.958647649478385</v>
+        <v>8.943704400695404</v>
       </c>
       <c r="P10" t="n">
-        <v>392.8786999628633</v>
+        <v>392.9033047033129</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35603,28 +35741,28 @@
         <v>0.0771</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6292050642655875</v>
+        <v>-0.6328393209806371</v>
       </c>
       <c r="J11" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K11" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1884848653858274</v>
+        <v>0.1911484370815704</v>
       </c>
       <c r="M11" t="n">
-        <v>7.21319846252411</v>
+        <v>7.198230495183114</v>
       </c>
       <c r="N11" t="n">
-        <v>90.43749244186213</v>
+        <v>90.19954345044968</v>
       </c>
       <c r="O11" t="n">
-        <v>9.509862903420959</v>
+        <v>9.497344020853919</v>
       </c>
       <c r="P11" t="n">
-        <v>389.5569769816722</v>
+        <v>389.5992027517732</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35681,28 +35819,28 @@
         <v>0.0854</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4711234920689596</v>
+        <v>-0.4748374181175079</v>
       </c>
       <c r="J12" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K12" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1486342888743488</v>
+        <v>0.1513201240675207</v>
       </c>
       <c r="M12" t="n">
-        <v>6.464429669911893</v>
+        <v>6.453031775457479</v>
       </c>
       <c r="N12" t="n">
-        <v>67.45445214366733</v>
+        <v>67.30641132434688</v>
       </c>
       <c r="O12" t="n">
-        <v>8.213065940540556</v>
+        <v>8.20404847159906</v>
       </c>
       <c r="P12" t="n">
-        <v>384.3536781310154</v>
+        <v>384.3968314009113</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35759,28 +35897,28 @@
         <v>0.102</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0636648735958955</v>
+        <v>-0.06463446301016783</v>
       </c>
       <c r="J13" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K13" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004897092698946337</v>
+        <v>0.005080607780136304</v>
       </c>
       <c r="M13" t="n">
-        <v>5.113247113566283</v>
+        <v>5.097554425352915</v>
       </c>
       <c r="N13" t="n">
-        <v>44.00521390258</v>
+        <v>43.847533152781</v>
       </c>
       <c r="O13" t="n">
-        <v>6.633642581763054</v>
+        <v>6.621746986466714</v>
       </c>
       <c r="P13" t="n">
-        <v>378.7848339198314</v>
+        <v>378.7960512982742</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35837,28 +35975,28 @@
         <v>0.0586</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.007457131582466557</v>
+        <v>-0.01010530317068076</v>
       </c>
       <c r="J14" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K14" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L14" t="n">
-        <v>5.990446828563201e-05</v>
+        <v>0.0001106417243477154</v>
       </c>
       <c r="M14" t="n">
-        <v>5.23601796062772</v>
+        <v>5.226276490380215</v>
       </c>
       <c r="N14" t="n">
-        <v>49.59445043152366</v>
+        <v>49.46253306244363</v>
       </c>
       <c r="O14" t="n">
-        <v>7.042332740755982</v>
+        <v>7.032960476388562</v>
       </c>
       <c r="P14" t="n">
-        <v>383.0840474932327</v>
+        <v>383.1146821912031</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35915,28 +36053,28 @@
         <v>0.0416</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.03416428071723326</v>
+        <v>-0.03222529662733054</v>
       </c>
       <c r="J15" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K15" t="n">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001938008556003568</v>
+        <v>0.001734972559004788</v>
       </c>
       <c r="M15" t="n">
-        <v>4.478764676728012</v>
+        <v>4.472179755969473</v>
       </c>
       <c r="N15" t="n">
-        <v>31.98676708704736</v>
+        <v>31.8959017700415</v>
       </c>
       <c r="O15" t="n">
-        <v>5.655684493237522</v>
+        <v>5.647645683826271</v>
       </c>
       <c r="P15" t="n">
-        <v>392.0098304830295</v>
+        <v>391.9873218937507</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35974,7 +36112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P532"/>
+  <dimension ref="A1:P534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79041,7 +79179,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>-40.72794637595407,172.3147618742557</t>
+          <t>-40.727958057859816,172.3147791188665</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -79123,7 +79261,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>-40.727913606697136,172.31471350094375</t>
+          <t>-40.727958057859816,172.3147791188665</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -79205,7 +79343,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>-40.727913606697136,172.31471350094375</t>
+          <t>-40.727958057859816,172.3147791188665</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -79287,7 +79425,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>-40.72788718759238,172.31467450165374</t>
+          <t>-40.72795590120049,172.31477593524562</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -79369,7 +79507,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>-40.72788718759238,172.31467450165374</t>
+          <t>-40.72795590120049,172.31477593524562</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -79451,7 +79589,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>-40.72788718759238,172.31467450165374</t>
+          <t>-40.72795590120049,172.31477593524562</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -79522,6 +79660,170 @@
       <c r="P532" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:18:43+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-40.727963749043745,172.31478752008937</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-40.72744467640009,172.31536914100397</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>-40.727134134457984,172.31625859918074</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-40.726698981521984,172.3169641145994</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>-40.726205045215536,172.31757293730033</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-40.7256839652508,172.31813982310996</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>-40.72514890560841,172.3186945723572</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>-40.724606322443584,172.3192378151916</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>-40.72409841973846,172.31983468520272</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>-40.72359538589415,172.3204408839545</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>-40.72306055550843,172.3209966532828</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>-40.722468866921695,172.3214567927732</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>-40.72190262967637,172.32198824919047</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>-40.72131081539051,172.32248719020876</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:18:39+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-40.72797399317331,172.3148026422941</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-40.72744066263715,172.3153632159531</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-40.72713287642388,172.3162567420705</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-40.726696884811865,172.31696101941955</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-40.72620230310838,172.31756869691918</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-40.72568368211803,172.31813936265962</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>-40.72514834056707,172.31869365016544</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>-40.7246049663511,172.3192356019419</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>-40.724094612470466,172.3198283776074</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>-40.723589839562045,172.32043155372088</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>-40.72305972368761,172.32099525362625</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>-40.722471362374144,172.32146099171678</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>-40.72190251130511,172.32198807066723</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>-40.721317030656216,172.32249559650333</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0317/nzd0317.xlsx
+++ b/data/nzd0317/nzd0317.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P534"/>
+  <dimension ref="A1:P540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29257,6 +29257,330 @@
         </is>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>424.33</v>
+      </c>
+      <c r="C535" t="n">
+        <v>426.46</v>
+      </c>
+      <c r="D535" t="n">
+        <v>391.37</v>
+      </c>
+      <c r="E535" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="F535" t="n">
+        <v>376.81</v>
+      </c>
+      <c r="G535" t="n">
+        <v>375.03</v>
+      </c>
+      <c r="H535" t="n">
+        <v>375.33</v>
+      </c>
+      <c r="I535" t="n">
+        <v>377.73</v>
+      </c>
+      <c r="J535" t="n">
+        <v>374.79</v>
+      </c>
+      <c r="K535" t="n">
+        <v>369.1</v>
+      </c>
+      <c r="L535" t="n">
+        <v>366.98</v>
+      </c>
+      <c r="M535" t="n">
+        <v>375.83</v>
+      </c>
+      <c r="N535" t="n">
+        <v>380.58</v>
+      </c>
+      <c r="O535" t="n">
+        <v>394.91</v>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:18:49+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>425.51</v>
+      </c>
+      <c r="C536" t="n">
+        <v>426.76</v>
+      </c>
+      <c r="D536" t="n">
+        <v>392.02</v>
+      </c>
+      <c r="E536" t="n">
+        <v>379.54</v>
+      </c>
+      <c r="F536" t="n">
+        <v>377.07</v>
+      </c>
+      <c r="G536" t="n">
+        <v>374.16</v>
+      </c>
+      <c r="H536" t="n">
+        <v>375.08</v>
+      </c>
+      <c r="I536" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="J536" t="n">
+        <v>375.86</v>
+      </c>
+      <c r="K536" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="L536" t="n">
+        <v>365.99</v>
+      </c>
+      <c r="M536" t="n">
+        <v>375.88</v>
+      </c>
+      <c r="N536" t="n">
+        <v>380.71</v>
+      </c>
+      <c r="O536" t="n">
+        <v>395.13</v>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>425.62</v>
+      </c>
+      <c r="C537" t="n">
+        <v>429.76</v>
+      </c>
+      <c r="D537" t="n">
+        <v>392.33</v>
+      </c>
+      <c r="E537" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="F537" t="n">
+        <v>377.37</v>
+      </c>
+      <c r="G537" t="n">
+        <v>373.85</v>
+      </c>
+      <c r="H537" t="n">
+        <v>374.97</v>
+      </c>
+      <c r="I537" t="n">
+        <v>378.32</v>
+      </c>
+      <c r="J537" t="n">
+        <v>375.97</v>
+      </c>
+      <c r="K537" t="n">
+        <v>368.08</v>
+      </c>
+      <c r="L537" t="n">
+        <v>365.94</v>
+      </c>
+      <c r="M537" t="n">
+        <v>376.21</v>
+      </c>
+      <c r="N537" t="n">
+        <v>381.41</v>
+      </c>
+      <c r="O537" t="n">
+        <v>395.34</v>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:19:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>426.79</v>
+      </c>
+      <c r="C538" t="n">
+        <v>430</v>
+      </c>
+      <c r="D538" t="n">
+        <v>392.95</v>
+      </c>
+      <c r="E538" t="n">
+        <v>380.68</v>
+      </c>
+      <c r="F538" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="G538" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="H538" t="n">
+        <v>374.44</v>
+      </c>
+      <c r="I538" t="n">
+        <v>377.85</v>
+      </c>
+      <c r="J538" t="n">
+        <v>375.97</v>
+      </c>
+      <c r="K538" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="L538" t="n">
+        <v>366.37</v>
+      </c>
+      <c r="M538" t="n">
+        <v>377.02</v>
+      </c>
+      <c r="N538" t="n">
+        <v>382.19</v>
+      </c>
+      <c r="O538" t="n">
+        <v>396.74</v>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>426.67</v>
+      </c>
+      <c r="C539" t="n">
+        <v>431.84</v>
+      </c>
+      <c r="D539" t="n">
+        <v>394.1</v>
+      </c>
+      <c r="E539" t="n">
+        <v>382.64</v>
+      </c>
+      <c r="F539" t="n">
+        <v>378.22</v>
+      </c>
+      <c r="G539" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="H539" t="n">
+        <v>373.98</v>
+      </c>
+      <c r="I539" t="n">
+        <v>378.26</v>
+      </c>
+      <c r="J539" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="K539" t="n">
+        <v>368.27</v>
+      </c>
+      <c r="L539" t="n">
+        <v>365.53</v>
+      </c>
+      <c r="M539" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="N539" t="n">
+        <v>381.79</v>
+      </c>
+      <c r="O539" t="n">
+        <v>395.9</v>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>428.34</v>
+      </c>
+      <c r="C540" t="n">
+        <v>434.01</v>
+      </c>
+      <c r="D540" t="n">
+        <v>394.87</v>
+      </c>
+      <c r="E540" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="F540" t="n">
+        <v>379.34</v>
+      </c>
+      <c r="G540" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="H540" t="n">
+        <v>374.06</v>
+      </c>
+      <c r="I540" t="n">
+        <v>378.57</v>
+      </c>
+      <c r="J540" t="n">
+        <v>377.23</v>
+      </c>
+      <c r="K540" t="n">
+        <v>367.76</v>
+      </c>
+      <c r="L540" t="n">
+        <v>365.21</v>
+      </c>
+      <c r="M540" t="n">
+        <v>376.89</v>
+      </c>
+      <c r="N540" t="n">
+        <v>382.05</v>
+      </c>
+      <c r="O540" t="n">
+        <v>395.87</v>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29268,7 +29592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B560"/>
+  <dimension ref="A1:B566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34871,6 +35195,66 @@
       </c>
       <c r="B560" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>
@@ -35039,28 +35423,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>1.399639216306093</v>
+        <v>1.365556894561402</v>
       </c>
       <c r="J2" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K2" t="n">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3047562375254229</v>
+        <v>0.295983396989685</v>
       </c>
       <c r="M2" t="n">
-        <v>11.70352168936567</v>
+        <v>11.76868950937853</v>
       </c>
       <c r="N2" t="n">
-        <v>239.5555341898392</v>
+        <v>239.9439049140744</v>
       </c>
       <c r="O2" t="n">
-        <v>15.47758166477694</v>
+        <v>15.49012281791447</v>
       </c>
       <c r="P2" t="n">
-        <v>405.2659876313965</v>
+        <v>405.6619278988535</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35117,28 +35501,28 @@
         <v>0.0436</v>
       </c>
       <c r="I3" t="n">
-        <v>1.129472192739746</v>
+        <v>1.166265482035675</v>
       </c>
       <c r="J3" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K3" t="n">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2097788424944168</v>
+        <v>0.2217051255420041</v>
       </c>
       <c r="M3" t="n">
-        <v>13.7284284104475</v>
+        <v>13.80334614294215</v>
       </c>
       <c r="N3" t="n">
-        <v>256.0367462682324</v>
+        <v>256.7690871630642</v>
       </c>
       <c r="O3" t="n">
-        <v>16.00114827967769</v>
+        <v>16.02401594991294</v>
       </c>
       <c r="P3" t="n">
-        <v>381.3391173607345</v>
+        <v>380.9101687385929</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35195,28 +35579,28 @@
         <v>0.0762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1092974102363326</v>
+        <v>0.1193637607037482</v>
       </c>
       <c r="J4" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K4" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007433117191984584</v>
+        <v>0.009004768170688293</v>
       </c>
       <c r="M4" t="n">
-        <v>7.375690064157758</v>
+        <v>7.355160003809481</v>
       </c>
       <c r="N4" t="n">
-        <v>84.90394970256378</v>
+        <v>84.23581091617346</v>
       </c>
       <c r="O4" t="n">
-        <v>9.214333926148095</v>
+        <v>9.178006914149361</v>
       </c>
       <c r="P4" t="n">
-        <v>385.0647053620334</v>
+        <v>384.9473223094421</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35273,28 +35657,28 @@
         <v>0.0934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.360734409066316</v>
+        <v>-0.359505346334292</v>
       </c>
       <c r="J5" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K5" t="n">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1141650499396646</v>
+        <v>0.1154737299656099</v>
       </c>
       <c r="M5" t="n">
-        <v>5.799752857425372</v>
+        <v>5.75322430682226</v>
       </c>
       <c r="N5" t="n">
-        <v>53.69462630175356</v>
+        <v>53.13440621059776</v>
       </c>
       <c r="O5" t="n">
-        <v>7.327661721296471</v>
+        <v>7.289335100720625</v>
       </c>
       <c r="P5" t="n">
-        <v>390.0220920329857</v>
+        <v>390.0076927833668</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35351,28 +35735,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4274959024041129</v>
+        <v>-0.4299234068293555</v>
       </c>
       <c r="J6" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K6" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1269531131685571</v>
+        <v>0.1304825095549391</v>
       </c>
       <c r="M6" t="n">
-        <v>6.122710882340565</v>
+        <v>6.063630667462813</v>
       </c>
       <c r="N6" t="n">
-        <v>66.89250741436608</v>
+        <v>66.16997162761452</v>
       </c>
       <c r="O6" t="n">
-        <v>8.178783981397606</v>
+        <v>8.134492708682854</v>
       </c>
       <c r="P6" t="n">
-        <v>390.4345864236318</v>
+        <v>390.4628648159292</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35429,28 +35813,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4159607985604809</v>
+        <v>-0.424527492276434</v>
       </c>
       <c r="J7" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K7" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1258409913188682</v>
+        <v>0.1323802980510851</v>
       </c>
       <c r="M7" t="n">
-        <v>6.030318224941505</v>
+        <v>5.99377528609222</v>
       </c>
       <c r="N7" t="n">
-        <v>63.97237336967645</v>
+        <v>63.45567047625693</v>
       </c>
       <c r="O7" t="n">
-        <v>7.998273149228929</v>
+        <v>7.96590675794394</v>
       </c>
       <c r="P7" t="n">
-        <v>389.0670482930295</v>
+        <v>389.1669366209184</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35507,28 +35891,28 @@
         <v>0.0761</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4459061543081422</v>
+        <v>-0.4564296375183112</v>
       </c>
       <c r="J8" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K8" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1379476701852816</v>
+        <v>0.1455782768812317</v>
       </c>
       <c r="M8" t="n">
-        <v>6.291577498971161</v>
+        <v>6.260455874272955</v>
       </c>
       <c r="N8" t="n">
-        <v>66.13411446734796</v>
+        <v>65.68650070237038</v>
       </c>
       <c r="O8" t="n">
-        <v>8.132288390566824</v>
+        <v>8.104720889849963</v>
       </c>
       <c r="P8" t="n">
-        <v>391.8150656680037</v>
+        <v>391.937759430777</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35585,28 +35969,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5516795307800613</v>
+        <v>-0.5546848133625374</v>
       </c>
       <c r="J9" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K9" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1884986658156077</v>
+        <v>0.1932886326221999</v>
       </c>
       <c r="M9" t="n">
-        <v>6.223936500481925</v>
+        <v>6.166334986818636</v>
       </c>
       <c r="N9" t="n">
-        <v>69.738732265999</v>
+        <v>68.98539570983624</v>
       </c>
       <c r="O9" t="n">
-        <v>8.350971935409614</v>
+        <v>8.305744741432658</v>
       </c>
       <c r="P9" t="n">
-        <v>394.4722623389672</v>
+        <v>394.5072914760916</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35663,28 +36047,28 @@
         <v>0.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6130210853393976</v>
+        <v>-0.6135696389061692</v>
       </c>
       <c r="J10" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K10" t="n">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2000529374453145</v>
+        <v>0.2036250833305512</v>
       </c>
       <c r="M10" t="n">
-        <v>6.697083186968561</v>
+        <v>6.629578821637055</v>
       </c>
       <c r="N10" t="n">
-        <v>79.98984840701834</v>
+        <v>79.10388756746987</v>
       </c>
       <c r="O10" t="n">
-        <v>8.943704400695404</v>
+        <v>8.894036629532726</v>
       </c>
       <c r="P10" t="n">
-        <v>392.9033047033129</v>
+        <v>392.9096822037056</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35741,28 +36125,28 @@
         <v>0.0771</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6328393209806371</v>
+        <v>-0.6412926954511016</v>
       </c>
       <c r="J11" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K11" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1911484370815704</v>
+        <v>0.1981938611428744</v>
       </c>
       <c r="M11" t="n">
-        <v>7.198230495183114</v>
+        <v>7.145695019445014</v>
       </c>
       <c r="N11" t="n">
-        <v>90.19954345044968</v>
+        <v>89.38085622491867</v>
       </c>
       <c r="O11" t="n">
-        <v>9.497344020853919</v>
+        <v>9.454144922991114</v>
       </c>
       <c r="P11" t="n">
-        <v>389.5992027517732</v>
+        <v>389.6977577797792</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35819,28 +36203,28 @@
         <v>0.0854</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4748374181175079</v>
+        <v>-0.4862579724868742</v>
       </c>
       <c r="J12" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K12" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1513201240675207</v>
+        <v>0.1595784131696324</v>
       </c>
       <c r="M12" t="n">
-        <v>6.453031775457479</v>
+        <v>6.420735346218819</v>
       </c>
       <c r="N12" t="n">
-        <v>67.30641132434688</v>
+        <v>66.8974051555452</v>
       </c>
       <c r="O12" t="n">
-        <v>8.20404847159906</v>
+        <v>8.179083393360481</v>
       </c>
       <c r="P12" t="n">
-        <v>384.3968314009113</v>
+        <v>384.5299820761059</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35897,28 +36281,28 @@
         <v>0.102</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06463446301016783</v>
+        <v>-0.06587281105516843</v>
       </c>
       <c r="J13" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K13" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005080607780136304</v>
+        <v>0.00538368479872342</v>
       </c>
       <c r="M13" t="n">
-        <v>5.097554425352915</v>
+        <v>5.045201406879651</v>
       </c>
       <c r="N13" t="n">
-        <v>43.847533152781</v>
+        <v>43.36611083872693</v>
       </c>
       <c r="O13" t="n">
-        <v>6.621746986466714</v>
+        <v>6.585295045685267</v>
       </c>
       <c r="P13" t="n">
-        <v>378.7960512982742</v>
+        <v>378.8104128127506</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35975,28 +36359,28 @@
         <v>0.0586</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01010530317068076</v>
+        <v>-0.01292080546240533</v>
       </c>
       <c r="J14" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K14" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001106417243477154</v>
+        <v>0.0001845115316200241</v>
       </c>
       <c r="M14" t="n">
-        <v>5.226276490380215</v>
+        <v>5.178503034569546</v>
       </c>
       <c r="N14" t="n">
-        <v>49.46253306244363</v>
+        <v>48.9370346505084</v>
       </c>
       <c r="O14" t="n">
-        <v>7.032960476388562</v>
+        <v>6.995501029269341</v>
       </c>
       <c r="P14" t="n">
-        <v>383.1146821912031</v>
+        <v>383.1473466411188</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36053,28 +36437,28 @@
         <v>0.0416</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.03222529662733054</v>
+        <v>-0.02298037307863937</v>
       </c>
       <c r="J15" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="K15" t="n">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001734972559004788</v>
+        <v>0.0008948603903505825</v>
       </c>
       <c r="M15" t="n">
-        <v>4.472179755969473</v>
+        <v>4.470605732524522</v>
       </c>
       <c r="N15" t="n">
-        <v>31.8959017700415</v>
+        <v>31.76559175276205</v>
       </c>
       <c r="O15" t="n">
-        <v>5.647645683826271</v>
+        <v>5.636097209307346</v>
       </c>
       <c r="P15" t="n">
-        <v>391.9873218937507</v>
+        <v>391.8796250946998</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36112,7 +36496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P534"/>
+  <dimension ref="A1:P540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79827,6 +80211,498 @@
         </is>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-40.727951647788785,172.31476965643833</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>-40.72742844162574,172.31534517550412</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>-40.72712820372555,172.3162498442332</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-40.72669544706774,172.31695889701064</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>-40.726198510832305,172.31756283256286</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-40.725682379707266,172.31813724458812</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>-40.72514884910428,172.318694480138</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>-40.72460315822774,172.31923265094247</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>-40.724088845578606,172.319818823457</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>-40.72358335035251,172.3204206373495</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>-40.72305672913251,172.32099021486283</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>-40.722469255103206,172.3214574459422</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>-40.721893574274716,172.32197459216536</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>-40.72130742524533,172.32248260495783</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:18:49+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-40.727944578737585,172.3147592212392</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>-40.72742664441796,172.31534252249745</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>-40.727124309809945,172.31624409603617</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-40.72668861778259,172.3169488155696</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>-40.72619699392176,172.31756048682053</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-40.725687306217395,172.31814525642423</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>-40.7251502617076,172.31869678561742</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>-40.72460135010427,172.31922969994318</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>-40.724082854728955,172.3198088982734</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>-40.72358690000572,172.3204266086977</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>-40.72306221915003,172.32099945259608</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>-40.7224689778307,172.3214569793929</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>-40.721892804861426,172.32197343176472</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>-40.72130604407503,172.32248073689277</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-40.727943919758175,172.31475824846652</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>-40.727408672336686,172.31531599243883</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>-40.72712245271164,172.31624135458858</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-40.726683765395265,172.31694165244167</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>-40.726195243640355,172.31755778019487</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-40.725689061640395,172.31814811121671</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>-40.725150883253036,172.31869780002842</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>-40.72459982450006,172.31922721003767</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>-40.72408223884716,172.31980787792756</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>-40.72358900761216,172.32043015418597</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>-40.72306249642362,172.3209999191483</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>-40.722467147832155,172.3214539001678</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>-40.7218886618666,172.32196718345395</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>-40.72130472568515,172.32247895373985</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:19:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>-40.72793691061319,172.31474790170367</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>-40.727407234569924,172.31531387003477</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>-40.727118738514825,172.3162358716939</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-40.726681788496585,172.3169387341306</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>-40.72619448518504,172.31755660732378</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>-40.725693082125105,172.31815464961295</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-40.725153877971856,172.31870268764519</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>-40.72460248018144,172.31923154431772</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>-40.72408223884716,172.31980787792756</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>-40.72358545795914,172.3204241828374</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>-40.723060111870666,172.3209959067993</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>-40.72246265601719,172.32144634207052</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>-40.721884045386275,172.32196022105143</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>-40.721295936418656,172.3224670660554</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>-40.72793762949989,172.31474896291002</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>-40.72739621169012,172.31529759827325</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>-40.72711184927814,172.31622570181017</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-40.72667004691508,172.31692140113503</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>-40.7261902845093,172.31755011142297</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>-40.725694554415185,172.31815704395544</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>-40.72515647716163,172.31870692972802</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>-40.72460016352321,172.31922776335</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>-40.72407742377106,172.31979990067865</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>-40.72358795380895,172.3204283814418</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>-40.723064770067005,172.3210037448767</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>-40.72246370965285,172.32144811495746</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>-40.72188641281214,172.32196379151412</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>-40.7213012099787,172.32247419866567</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>-40.72792762499233,172.31473419445715</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>-40.727383211877864,172.31527840821357</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>-40.72710723648437,172.31621889241094</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-40.72666333743879,172.31691149656888</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-40.72618375012409,172.31754000668997</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-40.725694441162105,172.31815685977523</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>-40.72515602512865,172.31870619197446</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>-40.72459841190351,172.3192249045697</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>-40.72407518420058,172.3197961903307</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>-40.72359078243855,172.32043313986048</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>-40.72306654461785,172.3210067308112</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>-40.72246337692581,172.32144755509844</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>-40.721884873985346,172.32196147071335</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>-40.72130139832012,172.32247445340178</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0317/nzd0317.xlsx
+++ b/data/nzd0317/nzd0317.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P540"/>
+  <dimension ref="A1:P544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29581,6 +29581,222 @@
         </is>
       </c>
     </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>426.81</v>
+      </c>
+      <c r="C541" t="n">
+        <v>433.24</v>
+      </c>
+      <c r="D541" t="n">
+        <v>394.78</v>
+      </c>
+      <c r="E541" t="n">
+        <v>383.29</v>
+      </c>
+      <c r="F541" t="n">
+        <v>378.78</v>
+      </c>
+      <c r="G541" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="H541" t="n">
+        <v>373.58</v>
+      </c>
+      <c r="I541" t="n">
+        <v>378.08</v>
+      </c>
+      <c r="J541" t="n">
+        <v>376.74</v>
+      </c>
+      <c r="K541" t="n">
+        <v>367.57</v>
+      </c>
+      <c r="L541" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="M541" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="N541" t="n">
+        <v>383.28</v>
+      </c>
+      <c r="O541" t="n">
+        <v>396.14</v>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:19:09+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>423.99</v>
+      </c>
+      <c r="C542" t="n">
+        <v>434.86</v>
+      </c>
+      <c r="D542" t="n">
+        <v>395.14</v>
+      </c>
+      <c r="E542" t="n">
+        <v>384.14</v>
+      </c>
+      <c r="F542" t="n">
+        <v>379.86</v>
+      </c>
+      <c r="G542" t="n">
+        <v>372.98</v>
+      </c>
+      <c r="H542" t="n">
+        <v>373.45</v>
+      </c>
+      <c r="I542" t="n">
+        <v>377.58</v>
+      </c>
+      <c r="J542" t="n">
+        <v>376.73</v>
+      </c>
+      <c r="K542" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="L542" t="n">
+        <v>364.17</v>
+      </c>
+      <c r="M542" t="n">
+        <v>373.51</v>
+      </c>
+      <c r="N542" t="n">
+        <v>382.05</v>
+      </c>
+      <c r="O542" t="n">
+        <v>395.62</v>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>423.2</v>
+      </c>
+      <c r="C543" t="n">
+        <v>433.37</v>
+      </c>
+      <c r="D543" t="n">
+        <v>394.76</v>
+      </c>
+      <c r="E543" t="n">
+        <v>383.4</v>
+      </c>
+      <c r="F543" t="n">
+        <v>379.21</v>
+      </c>
+      <c r="G543" t="n">
+        <v>372.73</v>
+      </c>
+      <c r="H543" t="n">
+        <v>373.06</v>
+      </c>
+      <c r="I543" t="n">
+        <v>377.03</v>
+      </c>
+      <c r="J543" t="n">
+        <v>376.22</v>
+      </c>
+      <c r="K543" t="n">
+        <v>367.12</v>
+      </c>
+      <c r="L543" t="n">
+        <v>364.01</v>
+      </c>
+      <c r="M543" t="n">
+        <v>373.25</v>
+      </c>
+      <c r="N543" t="n">
+        <v>381.86</v>
+      </c>
+      <c r="O543" t="n">
+        <v>395.07</v>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>422.91</v>
+      </c>
+      <c r="C544" t="n">
+        <v>435.12</v>
+      </c>
+      <c r="D544" t="n">
+        <v>394.79</v>
+      </c>
+      <c r="E544" t="n">
+        <v>384.17</v>
+      </c>
+      <c r="F544" t="n">
+        <v>380.27</v>
+      </c>
+      <c r="G544" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="H544" t="n">
+        <v>373.12</v>
+      </c>
+      <c r="I544" t="n">
+        <v>377.28</v>
+      </c>
+      <c r="J544" t="n">
+        <v>376.3</v>
+      </c>
+      <c r="K544" t="n">
+        <v>366.83</v>
+      </c>
+      <c r="L544" t="n">
+        <v>363.03</v>
+      </c>
+      <c r="M544" t="n">
+        <v>372.28</v>
+      </c>
+      <c r="N544" t="n">
+        <v>381.07</v>
+      </c>
+      <c r="O544" t="n">
+        <v>394.58</v>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29592,7 +29808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B566"/>
+  <dimension ref="A1:B570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35255,6 +35471,46 @@
       </c>
       <c r="B566" t="n">
         <v>-0.8</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>
@@ -35423,28 +35679,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>1.365556894561402</v>
+        <v>1.340947457242191</v>
       </c>
       <c r="J2" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K2" t="n">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="L2" t="n">
-        <v>0.295983396989685</v>
+        <v>0.2890978005479683</v>
       </c>
       <c r="M2" t="n">
-        <v>11.76868950937853</v>
+        <v>11.82204848880477</v>
       </c>
       <c r="N2" t="n">
-        <v>239.9439049140744</v>
+        <v>240.6325171704247</v>
       </c>
       <c r="O2" t="n">
-        <v>15.49012281791447</v>
+        <v>15.51233435593833</v>
       </c>
       <c r="P2" t="n">
-        <v>405.6619278988535</v>
+        <v>405.9491679256391</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35501,28 +35757,28 @@
         <v>0.0436</v>
       </c>
       <c r="I3" t="n">
-        <v>1.166265482035675</v>
+        <v>1.195453238834543</v>
       </c>
       <c r="J3" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K3" t="n">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2217051255420041</v>
+        <v>0.2303762733440932</v>
       </c>
       <c r="M3" t="n">
-        <v>13.80334614294215</v>
+        <v>13.88213456640471</v>
       </c>
       <c r="N3" t="n">
-        <v>256.7690871630642</v>
+        <v>258.2831496094558</v>
       </c>
       <c r="O3" t="n">
-        <v>16.02401594991294</v>
+        <v>16.07119004957181</v>
       </c>
       <c r="P3" t="n">
-        <v>380.9101687385929</v>
+        <v>380.568397466701</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35579,28 +35835,28 @@
         <v>0.0762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1193637607037482</v>
+        <v>0.12836812708081</v>
       </c>
       <c r="J4" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K4" t="n">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009004768170688293</v>
+        <v>0.01049898299246776</v>
       </c>
       <c r="M4" t="n">
-        <v>7.355160003809481</v>
+        <v>7.356339843507003</v>
       </c>
       <c r="N4" t="n">
-        <v>84.23581091617346</v>
+        <v>83.93803692629687</v>
       </c>
       <c r="O4" t="n">
-        <v>9.178006914149361</v>
+        <v>9.161770403491722</v>
       </c>
       <c r="P4" t="n">
-        <v>384.9473223094421</v>
+        <v>384.8418813005163</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35657,28 +35913,28 @@
         <v>0.0934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.359505346334292</v>
+        <v>-0.3548311756187895</v>
       </c>
       <c r="J5" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K5" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1154737299656099</v>
+        <v>0.114008580561479</v>
       </c>
       <c r="M5" t="n">
-        <v>5.75322430682226</v>
+        <v>5.742475098048487</v>
       </c>
       <c r="N5" t="n">
-        <v>53.13440621059776</v>
+        <v>52.82931359521373</v>
       </c>
       <c r="O5" t="n">
-        <v>7.289335100720625</v>
+        <v>7.268377645335562</v>
       </c>
       <c r="P5" t="n">
-        <v>390.0076927833668</v>
+        <v>389.952862115837</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35735,28 +35991,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4299234068293555</v>
+        <v>-0.4289860431429296</v>
       </c>
       <c r="J6" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K6" t="n">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1304825095549391</v>
+        <v>0.1315057995955167</v>
       </c>
       <c r="M6" t="n">
-        <v>6.063630667462813</v>
+        <v>6.026406518893708</v>
       </c>
       <c r="N6" t="n">
-        <v>66.16997162761452</v>
+        <v>65.68765042088425</v>
       </c>
       <c r="O6" t="n">
-        <v>8.134492708682854</v>
+        <v>8.104791818479008</v>
       </c>
       <c r="P6" t="n">
-        <v>390.4628648159292</v>
+        <v>390.4518763465193</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35813,28 +36069,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.424527492276434</v>
+        <v>-0.4311351027371816</v>
       </c>
       <c r="J7" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K7" t="n">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1323802980510851</v>
+        <v>0.1372278779586766</v>
       </c>
       <c r="M7" t="n">
-        <v>5.99377528609222</v>
+        <v>5.973216228021522</v>
       </c>
       <c r="N7" t="n">
-        <v>63.45567047625693</v>
+        <v>63.16200538917757</v>
       </c>
       <c r="O7" t="n">
-        <v>7.96590675794394</v>
+        <v>7.947452761053542</v>
       </c>
       <c r="P7" t="n">
-        <v>389.1669366209184</v>
+        <v>389.2443082509218</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35891,28 +36147,28 @@
         <v>0.0761</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4564296375183112</v>
+        <v>-0.4648947443178036</v>
       </c>
       <c r="J8" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K8" t="n">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1455782768812317</v>
+        <v>0.1513702344217136</v>
       </c>
       <c r="M8" t="n">
-        <v>6.260455874272955</v>
+        <v>6.245219263435123</v>
       </c>
       <c r="N8" t="n">
-        <v>65.68650070237038</v>
+        <v>65.48810682324834</v>
       </c>
       <c r="O8" t="n">
-        <v>8.104720889849963</v>
+        <v>8.092472231849074</v>
       </c>
       <c r="P8" t="n">
-        <v>391.937759430777</v>
+        <v>392.0368892586604</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35969,28 +36225,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5546848133625374</v>
+        <v>-0.5573897602067005</v>
       </c>
       <c r="J9" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K9" t="n">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1932886326221999</v>
+        <v>0.1968582746661935</v>
       </c>
       <c r="M9" t="n">
-        <v>6.166334986818636</v>
+        <v>6.131269617335852</v>
       </c>
       <c r="N9" t="n">
-        <v>68.98539570983624</v>
+        <v>68.50651461261074</v>
       </c>
       <c r="O9" t="n">
-        <v>8.305744741432658</v>
+        <v>8.276866231407316</v>
       </c>
       <c r="P9" t="n">
-        <v>394.5072914760916</v>
+        <v>394.538972480931</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36047,28 +36303,28 @@
         <v>0.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6135696389061692</v>
+        <v>-0.6133210755563409</v>
       </c>
       <c r="J10" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K10" t="n">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2036250833305512</v>
+        <v>0.2056785208119609</v>
       </c>
       <c r="M10" t="n">
-        <v>6.629578821637055</v>
+        <v>6.582546306722475</v>
       </c>
       <c r="N10" t="n">
-        <v>79.10388756746987</v>
+        <v>78.51963707873402</v>
       </c>
       <c r="O10" t="n">
-        <v>8.894036629532726</v>
+        <v>8.861130688503247</v>
       </c>
       <c r="P10" t="n">
-        <v>392.9096822037056</v>
+        <v>392.9067732769435</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36125,28 +36381,28 @@
         <v>0.0771</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6412926954511016</v>
+        <v>-0.6481495501371072</v>
       </c>
       <c r="J11" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K11" t="n">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1981938611428744</v>
+        <v>0.2034250782048669</v>
       </c>
       <c r="M11" t="n">
-        <v>7.145695019445014</v>
+        <v>7.115544455919881</v>
       </c>
       <c r="N11" t="n">
-        <v>89.38085622491867</v>
+        <v>88.90945981080216</v>
       </c>
       <c r="O11" t="n">
-        <v>9.454144922991114</v>
+        <v>9.429181290589453</v>
       </c>
       <c r="P11" t="n">
-        <v>389.6977577797792</v>
+        <v>389.7780570419367</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36203,28 +36459,28 @@
         <v>0.0854</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4862579724868742</v>
+        <v>-0.4960561937031506</v>
       </c>
       <c r="J12" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K12" t="n">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1595784131696324</v>
+        <v>0.1660567361162846</v>
       </c>
       <c r="M12" t="n">
-        <v>6.420735346218819</v>
+        <v>6.407939827134914</v>
       </c>
       <c r="N12" t="n">
-        <v>66.8974051555452</v>
+        <v>66.79087706064483</v>
       </c>
       <c r="O12" t="n">
-        <v>8.179083393360481</v>
+        <v>8.172568571792153</v>
       </c>
       <c r="P12" t="n">
-        <v>384.5299820761059</v>
+        <v>384.6447360149394</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36281,28 +36537,28 @@
         <v>0.102</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06587281105516843</v>
+        <v>-0.07069986271706803</v>
       </c>
       <c r="J13" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K13" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00538368479872342</v>
+        <v>0.006265335529354599</v>
       </c>
       <c r="M13" t="n">
-        <v>5.045201406879651</v>
+        <v>5.025426904533504</v>
       </c>
       <c r="N13" t="n">
-        <v>43.36611083872693</v>
+        <v>43.14571848977509</v>
       </c>
       <c r="O13" t="n">
-        <v>6.585295045685267</v>
+        <v>6.568540057712603</v>
       </c>
       <c r="P13" t="n">
-        <v>378.8104128127506</v>
+        <v>378.8667099718213</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36359,28 +36615,28 @@
         <v>0.0586</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01292080546240533</v>
+        <v>-0.01390596865047638</v>
       </c>
       <c r="J14" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K14" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001845115316200241</v>
+        <v>0.0002165611267795908</v>
       </c>
       <c r="M14" t="n">
-        <v>5.178503034569546</v>
+        <v>5.145777975085852</v>
       </c>
       <c r="N14" t="n">
-        <v>48.9370346505084</v>
+        <v>48.58502011221202</v>
       </c>
       <c r="O14" t="n">
-        <v>6.995501029269341</v>
+        <v>6.970295554150629</v>
       </c>
       <c r="P14" t="n">
-        <v>383.1473466411188</v>
+        <v>383.1588500696415</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36437,28 +36693,28 @@
         <v>0.0416</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02298037307863937</v>
+        <v>-0.01747969605349214</v>
       </c>
       <c r="J15" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K15" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0008948603903505825</v>
+        <v>0.0005228716065653893</v>
       </c>
       <c r="M15" t="n">
-        <v>4.470605732524522</v>
+        <v>4.466607329940668</v>
       </c>
       <c r="N15" t="n">
-        <v>31.76559175276205</v>
+        <v>31.65428769157892</v>
       </c>
       <c r="O15" t="n">
-        <v>5.636097209307346</v>
+        <v>5.626214330398276</v>
       </c>
       <c r="P15" t="n">
-        <v>391.8796250946998</v>
+        <v>391.8152763802519</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36496,7 +36752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P540"/>
+  <dimension ref="A1:P544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80703,6 +80959,334 @@
         </is>
       </c>
     </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>-40.72793679079872,172.31474772483597</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>-40.727387824714846,172.31528521758875</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>-40.72710777564211,172.3162196883147</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-40.7266661530227,172.3169156529491</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-40.72618701731681,172.31754505905621</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-40.72569676285022,172.31816063546935</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-40.72515873732651,172.318710618496</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>-40.7246011805927,172.31922942328703</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>-40.72407792767439,172.31980073550696</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>-40.72359183624169,172.3204349126048</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>-40.723066710981996,172.3210070107426</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>-40.72247579873365,172.32146845650615</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>-40.72187759415024,172.32195049154186</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>-40.7212997032473,172.3224721607769</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:19:09+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>-40.72795368463387,172.314772663191</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>-40.72737811978466,172.315270891372</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>-40.727105619011134,172.31621650469978</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-40.726661061009125,172.3169081360915</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>-40.72618071630208,172.31753531520746</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>-40.72569398814977,172.31815612305448</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>-40.725159471880076,172.31871181734562</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>-40.72460400578558,172.31923403422343</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>-40.72407798366365,172.31980082826567</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>-40.72359222448493,172.32043556572114</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>-40.723072311907586,172.32101643509955</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>-40.72248212054513,172.32147909383275</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>-40.721884873985346,172.32196147071335</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>-40.72130296783195,172.3224765762027</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-40.72795841730304,172.31477964947</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-40.72738704592422,172.3152840679539</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-40.727107895454935,172.31621986518223</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-40.72666549405628,172.3169146801792</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-40.72618450857956,172.31754117956066</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-40.72569540381329,172.3181584253069</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-40.725161675540676,172.31871541389472</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>-40.724607113497505,172.31923910625395</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>-40.72408083911579,172.31980555895973</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>-40.72359433209112,172.32043911121</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>-40.723073199182856,172.32101792806714</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>-40.72248356236165,172.32148151988994</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>-40.72188599851262,172.32196316668313</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>-40.721306420757834,172.32248124636507</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-40.72796015461187,172.3147822140537</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-40.72737656220311,172.31526859210302</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-40.72710771573568,172.31621959988095</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-40.72666088129101,172.3169078707907</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-40.72617832424999,172.31753161615424</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-40.725694441162105,172.31815685977523</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>-40.72516133651598,172.31871486057943</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>-40.7246057009012,172.3192368007855</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>-40.724080391201745,172.31980481689004</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>-40.72359594052734,172.32044181697793</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>-40.72307863374348,172.32102707249445</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>-40.72248894144592,172.32149057095052</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>-40.72189067417842,172.32197021834764</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>-40.72130949700074,172.32248540705558</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
